--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>710668.6082165281</v>
+        <v>710669</v>
       </c>
       <c r="R2" t="n">
-        <v>6392144.112941504</v>
+        <v>6392144</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>1984-06-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1984-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>99330</v>
+        <v>99336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>99336</v>
+        <v>99339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>99339</v>
+        <v>99344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>99344</v>
+        <v>99345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>99345</v>
+        <v>99372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>99372</v>
+        <v>99378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>99378</v>
+        <v>99385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>99385</v>
+        <v>99389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>99389</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>99399</v>
+        <v>99404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106571389</v>
       </c>
       <c r="B2" t="n">
-        <v>99404</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106571389</v>
+        <v>72871110</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>108116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222361</v>
+        <v>220079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Malmhagen, Kullingbos 1:31, Gtl</t>
+          <t>Malmen-Krampbro, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>710669</v>
+        <v>710478</v>
       </c>
       <c r="R2" t="n">
-        <v>6392144</v>
+        <v>6392321</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1984-06-11</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1984-06-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>. Stig Högström: Sphagnum på gotland.</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,25 +757,243 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Källmyrartad fuktig skogsmark.</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>106571389</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Malmhagen, Kullingbos 1:31, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>710669</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6392144</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Källunge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1984-06-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1984-06-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>. Stig Högström: Sphagnum på gotland.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Källmyrartad fuktig skogsmark.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Stig Högström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>72871113</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Malmen-Krampbro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>710478</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6392321</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Källunge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera exemplar, finns i hela väggrenen.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 61561-2023 artfynd.xlsx
+++ b/artfynd/A 61561-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72871110</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106571389</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,8 +1011,18 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72871113</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>